--- a/result.xlsx
+++ b/result.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,12 +533,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>yolov8n-seg-carafe_seed42</t>
+          <t>yolov8n-seg-ema_seed42</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D:\yolov8-0301\ultralytics-main\runs\segment\yolov8n-seg-carafe_seed42\weights\best.pt</t>
+          <t>D:\yolov8-0301\ultralytics-main\runs\segment\0421ema\yolov8n-seg-ema_seed42\weights\best.pt</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -553,49 +553,253 @@
         <v>1036</v>
       </c>
       <c r="F2" t="n">
-        <v>3608843</v>
+        <v>3287667</v>
       </c>
       <c r="G2" t="n">
-        <v>12.161</v>
+        <v>11.76</v>
       </c>
       <c r="H2" t="n">
-        <v>5.096</v>
+        <v>3.447</v>
       </c>
       <c r="I2" t="n">
-        <v>196.221</v>
+        <v>290.133</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8850736585556398</v>
+        <v>0.8535773378640042</v>
       </c>
       <c r="K2" t="n">
+        <v>0.7427606882294373</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8049791775360338</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6457667080552151</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.7458027706822246</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.6496138996138996</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.622517656548035</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.2053040834310396</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.5906003707554038</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.9885826730840782</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.789591521919741</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>yolov8n-seg-gsneck_seed42</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>D:\yolov8-0301\ultralytics-main\runs\segment\0421ema\yolov8n-seg-gsneck_seed42\weights\best.pt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>806</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1036</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2797251</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10.603</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="I3" t="n">
+        <v>331.14</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.858289677716344</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.7403474903474904</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.7957843250660656</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.6479641868853734</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.7475065250515225</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.6447876447876448</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.6173738359997358</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.2122969028774916</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.5851069522924173</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.9882202144291492</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.7866635833607832</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>yolov8n-seg-pconv-gsneck-ema_seed42</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D:\yolov8-0301\ultralytics-main\runs\segment\0421ema\yolov8n-seg-pconv-gsneck-ema_seed42\weights\best.pt</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>806</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1036</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2460579</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9.834</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.468</v>
+      </c>
+      <c r="I4" t="n">
+        <v>288.316</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8676598031236876</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.7657437214841822</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8206138529854183</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.6625799077961932</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.7990615453760762</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.6476833976833977</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.658329805546287</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.2125754892221317</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.5692123814678558</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.9873381920812906</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.7782752867745732</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>yolov8n-seg_seed42</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D:\yolov8-0301\ultralytics-main\runs\segment\0421ema\yolov8n-seg_seed42\weights\best.pt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>806</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1036</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3263811</v>
+      </c>
+      <c r="G5" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>322.553</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8725244359024177</v>
+      </c>
+      <c r="K5" t="n">
         <v>0.750965250965251</v>
       </c>
-      <c r="L2" t="n">
-        <v>0.8049243314495989</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.6475753289891036</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.7815496188017025</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.6631274131274131</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.6323470050837596</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.2150601441277234</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.5469537907842744</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.98577083999199</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.7663623153881323</v>
+      <c r="L5" t="n">
+        <v>0.7993875497282223</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.6403861457729499</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.7834033953560012</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.6737451737451737</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.6480741516813777</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.2178848880757692</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.6030711733779029</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.9890065717617731</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.796038872569838</v>
       </c>
     </row>
   </sheetData>

--- a/result.xlsx
+++ b/result.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,12 +533,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>yolov8n-seg-ema_seed42</t>
+          <t>yolov8n-seg-spd-dsc-backbone_seed43</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D:\yolov8-0301\ultralytics-main\runs\segment\0421ema\yolov8n-seg-ema_seed42\weights\best.pt</t>
+          <t>D:\yolov8-0301\ultralytics-main\runs\segment\yolov8n-seg-spd-dsc-backbone_seed43\weights\best.pt</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -553,253 +553,49 @@
         <v>1036</v>
       </c>
       <c r="F2" t="n">
-        <v>3287667</v>
+        <v>3375439</v>
       </c>
       <c r="G2" t="n">
-        <v>11.76</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>3.447</v>
+        <v>3.292</v>
       </c>
       <c r="I2" t="n">
-        <v>290.133</v>
+        <v>303.783</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8535773378640042</v>
+        <v>0.8680179108903682</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7427606882294373</v>
+        <v>0.7617900234025393</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8049791775360338</v>
+        <v>0.8186617585448343</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6457667080552151</v>
+        <v>0.6558722736359894</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7458027706822246</v>
+        <v>0.773976258414625</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6496138996138996</v>
+        <v>0.6775911034096938</v>
       </c>
       <c r="P2" t="n">
-        <v>0.622517656548035</v>
+        <v>0.6645161266551695</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2053040834310396</v>
+        <v>0.2190426615288261</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5906003707554038</v>
+        <v>0.5658286283921464</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9885826730840782</v>
+        <v>0.9869146712778374</v>
       </c>
       <c r="T2" t="n">
-        <v>0.789591521919741</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>yolov8n-seg-gsneck_seed42</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>D:\yolov8-0301\ultralytics-main\runs\segment\0421ema\yolov8n-seg-gsneck_seed42\weights\best.pt</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>806</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1036</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2797251</v>
-      </c>
-      <c r="G3" t="n">
-        <v>10.603</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="I3" t="n">
-        <v>331.14</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.858289677716344</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.7403474903474904</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.7957843250660656</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.6479641868853734</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.7475065250515225</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.6447876447876448</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.6173738359997358</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.2122969028774916</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.5851069522924173</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.9882202144291492</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.7866635833607832</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>yolov8n-seg-pconv-gsneck-ema_seed42</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>D:\yolov8-0301\ultralytics-main\runs\segment\0421ema\yolov8n-seg-pconv-gsneck-ema_seed42\weights\best.pt</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>806</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1036</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2460579</v>
-      </c>
-      <c r="G4" t="n">
-        <v>9.834</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.468</v>
-      </c>
-      <c r="I4" t="n">
-        <v>288.316</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.8676598031236876</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.7657437214841822</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.8206138529854183</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.6625799077961932</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.7990615453760762</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.6476833976833977</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.658329805546287</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.2125754892221317</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.5692123814678558</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.9873381920812906</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.7782752867745732</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>yolov8n-seg_seed42</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>D:\yolov8-0301\ultralytics-main\runs\segment\0421ema\yolov8n-seg_seed42\weights\best.pt</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>806</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1036</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3263811</v>
-      </c>
-      <c r="G5" t="n">
-        <v>11.48</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>322.553</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.8725244359024177</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.750965250965251</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.7993875497282223</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.6403861457729499</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.7834033953560012</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.6737451737451737</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.6480741516813777</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.2178848880757692</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.6030711733779029</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.9890065717617731</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.796038872569838</v>
+        <v>0.776371649834992</v>
       </c>
     </row>
   </sheetData>
